--- a/docs/downloads/08/tbl_produits_elevage_marovoay_ampijoroa.xlsx
+++ b/docs/downloads/08/tbl_produits_elevage_marovoay_ampijoroa.xlsx
@@ -502,9 +502,6 @@
           <t>Trondro Nompian</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -516,9 +513,6 @@
         <is>
           <t>Vorona</t>
         </is>
-      </c>
-      <c r="C11">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
